--- a/artfynd/A 31592-2025 artfynd.xlsx
+++ b/artfynd/A 31592-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120215824</v>
+        <v>120215821</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554587</v>
+        <v>554648</v>
       </c>
       <c r="R2" t="n">
-        <v>6952881</v>
+        <v>6952884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +760,14 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>140-årig grannaturskog i örtrik bäckkant</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120215817</v>
+        <v>120215819</v>
       </c>
       <c r="B3" t="n">
-        <v>86426</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1988</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554731</v>
+        <v>554665</v>
       </c>
       <c r="R3" t="n">
-        <v>6952799</v>
+        <v>6952861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +873,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>drygt 100-årig grannaturskog i örtrik bäckkant</t>
+          <t>140-årig grannaturskog i örtrik bäckkant</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # klen förrötad granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120215826</v>
+        <v>120215824</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1968</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554618</v>
+        <v>554587</v>
       </c>
       <c r="R4" t="n">
-        <v>6952867</v>
+        <v>6952881</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,15 +987,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>gammal hänglavsrik grannaturskog på höjd</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>140-årig grannaturskog i örtrik bäckkant</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120215818</v>
+        <v>120215817</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1988</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554635</v>
+        <v>554731</v>
       </c>
       <c r="R5" t="n">
-        <v>6952829</v>
+        <v>6952799</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,15 +1093,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gammal hänglavsrik grannaturskog på höjd, kant mot contorta</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal sälg</t>
+          <t>drygt 100-årig grannaturskog i örtrik bäckkant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1135,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120215819</v>
+        <v>120215818</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554665</v>
+        <v>554635</v>
       </c>
       <c r="R6" t="n">
-        <v>6952861</v>
+        <v>6952829</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1199,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>140-årig grannaturskog i örtrik bäckkant</t>
+          <t>gammal hänglavsrik grannaturskog på höjd, kant mot contorta</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1232,7 +1207,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # klen förrötad granlåga</t>
+          <t>1 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1254,15 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120215821</v>
+        <v>120215826</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554648</v>
+        <v>554618</v>
       </c>
       <c r="R7" t="n">
-        <v>6952884</v>
+        <v>6952867</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1313,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig grannaturskog i örtrik bäckkant</t>
+          <t>gammal hänglavsrik grannaturskog på höjd</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1351,7 +1321,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+          <t>1 substratenheter # gammal sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 31592-2025 artfynd.xlsx
+++ b/artfynd/A 31592-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215821</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215819</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,8 +1370,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120215826</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>